--- a/uav_px4_dataset_project/eda_outputs/feature_selection_evidence_report.xlsx
+++ b/uav_px4_dataset_project/eda_outputs/feature_selection_evidence_report.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>is_leakage_or_non_model</t>
+          <t>cols_to_exclude</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4265,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4746,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5042,7 +5042,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6041,7 +6041,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6522,7 +6522,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6596,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6855,7 +6855,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6892,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7077,7 +7077,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7188,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7780,7 +7780,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8705,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8742,7 +8742,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9001,7 +9001,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9075,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9482,7 +9482,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9641,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9863,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -9889,7 +9889,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -9937,7 +9937,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -9963,7 +9963,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -10148,7 +10148,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10233,7 +10233,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10640,7 +10640,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -10777,7 +10777,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10788,7 +10788,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="B283" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10936,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11010,7 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>99.50634227358304</v>
+        <v>99.52007296739733</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -11184,18 +11184,18 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>battery_status__custom_faults</t>
+          <t>battery_status__full_charge_capacity_wh</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -11221,18 +11221,18 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>battery_status__full_charge_capacity_wh</t>
+          <t>battery_status__remaining_capacity_wh</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -11258,18 +11258,18 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>battery_status__remaining_capacity_wh</t>
+          <t>battery_status__is_required</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -11295,18 +11295,18 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>battery_status__is_required</t>
+          <t>battery_status__custom_faults</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>97.02442456783157</v>
+        <v>97.10718781247256</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -11332,18 +11332,18 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>battery_status__available_energy</t>
+          <t>battery_status__voltage_cell_v[11]</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11380,7 +11380,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11417,7 +11417,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -11443,18 +11443,18 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>battery_status__voltage_cell_v[12]</t>
+          <t>battery_status__voltage_cell_v[13]</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -11480,18 +11480,18 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>battery_status__voltage_cell_v[11]</t>
+          <t>battery_status__voltage_cell_v[12]</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11602,7 +11602,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -11702,18 +11702,18 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>battery_status__voltage_cell_v[13]</t>
+          <t>battery_status__available_energy</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>96.53076684141465</v>
+        <v>96.62726077986987</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -11739,18 +11739,18 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>battery_status__interface_error</t>
+          <t>battery_status_1__voltage_cell_v[3]</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>95.8160328619153</v>
+        <v>96.27521157617898</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -11776,18 +11776,18 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>battery_status__manufacture_date</t>
+          <t>battery_status_1__voltage_cell_v[0]</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>95.8160328619153</v>
+        <v>96.27521157617898</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -11813,18 +11813,18 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>battery_status_1__voltage_cell_v[0]</t>
+          <t>battery_status_1__voltage_cell_v[1]</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>95.43410184404536</v>
+        <v>96.27521157617898</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -11850,18 +11850,18 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>battery_status_1__voltage_cell_v[1]</t>
+          <t>battery_status_1__voltage_cell_v[2]</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>95.43410184404536</v>
+        <v>96.27521157617898</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -11887,18 +11887,18 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>battery_status_1__voltage_cell_v[2]</t>
+          <t>battery_status_1__max_cell_voltage_delta</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>95.43410184404536</v>
+        <v>96.27521157617898</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -11924,18 +11924,18 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>battery_status_1__max_cell_voltage_delta</t>
+          <t>battery_status__manufacture_date</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>95.43410184404536</v>
+        <v>95.93240655289135</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -11961,18 +11961,18 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>battery_status_1__voltage_cell_v[3]</t>
+          <t>battery_status__interface_error</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>95.43410184404536</v>
+        <v>95.93240655289135</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12009,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>91.34490431122465</v>
+        <v>90.98214794694456</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12046,7 +12046,7 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12083,7 +12083,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12120,7 +12120,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12194,7 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12231,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>90.18738391515743</v>
+        <v>90.46031396318043</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>88.06853839278357</v>
+        <v>88.4004024299869</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12490,7 +12490,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12527,7 +12527,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12601,7 +12601,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>87.58708344162636</v>
+        <v>88.04296078772744</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12638,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>83.74606183162072</v>
+        <v>84.30877411382976</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12675,7 +12675,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -12749,7 +12749,7 @@
         </is>
       </c>
       <c r="B333" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -12757,7 +12757,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>23567</v>
+        <v>22356</v>
       </c>
       <c r="E333" t="inlineStr"/>
       <c r="F333" t="inlineStr"/>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12786,7 +12786,7 @@
         </is>
       </c>
       <c r="B334" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="B335" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12897,7 +12897,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12934,7 +12934,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="B341" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Removed: high missing values</t>
+          <t>Removed: &gt;80% missing</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>81.25416003702036</v>
+        <v>82.71307450655335</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13156,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>73.60080126274953</v>
+        <v>75.04918674322903</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -13167,19 +13167,19 @@
         <v>9842</v>
       </c>
       <c r="E344" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="F344" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="G344" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="H344" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="I344" t="n">
-        <v>0.2633294106956012</v>
+        <v>0.2615885039095251</v>
       </c>
       <c r="J344" t="b">
         <v>1</v>
@@ -13192,7 +13192,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13203,7 +13203,7 @@
         </is>
       </c>
       <c r="B345" t="n">
-        <v>73.60080126274953</v>
+        <v>75.04918674322903</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -13214,19 +13214,19 @@
         <v>9842</v>
       </c>
       <c r="E345" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="F345" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="G345" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="H345" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="I345" t="n">
-        <v>0.2624205663868999</v>
+        <v>0.2615473102205008</v>
       </c>
       <c r="J345" t="b">
         <v>1</v>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>73.60080126274953</v>
+        <v>75.04918674322903</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -13261,19 +13261,19 @@
         <v>9842</v>
       </c>
       <c r="E346" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="F346" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="G346" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="H346" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="I346" t="n">
-        <v>0.262630424500139</v>
+        <v>0.2600280886623072</v>
       </c>
       <c r="J346" t="b">
         <v>1</v>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>73.60080126274953</v>
+        <v>75.04918674322903</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -13308,19 +13308,19 @@
         <v>9842</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="F347" t="n">
-        <v>0.1275320767710299</v>
+        <v>0.1271893500124146</v>
       </c>
       <c r="G347" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="H347" t="n">
-        <v>0.3050131422495272</v>
+        <v>0.3221719961076597</v>
       </c>
       <c r="I347" t="n">
-        <v>0.2620662696126321</v>
+        <v>0.2603016541114562</v>
       </c>
       <c r="J347" t="b">
         <v>1</v>
@@ -13333,7 +13333,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13344,7 +13344,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>73.60080126274953</v>
+        <v>75.04918674322903</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>57.91373747234566</v>
+        <v>55.15078028586087</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13418,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>41.9345994637118</v>
+        <v>40.33020212400451</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="B351" t="n">
-        <v>41.44094173729485</v>
+        <v>39.85027509140183</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>38.46536630512644</v>
+        <v>36.95746290387439</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
         </is>
       </c>
       <c r="B353" t="n">
-        <v>38.46536630512644</v>
+        <v>36.95746290387439</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13566,7 +13566,7 @@
         </is>
       </c>
       <c r="B354" t="n">
-        <v>38.46536630512644</v>
+        <v>36.95746290387439</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13603,7 +13603,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>38.46536630512644</v>
+        <v>36.95746290387439</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>33.93734429575724</v>
+        <v>32.55538419584104</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>18.35107225944685</v>
+        <v>17.42173645766088</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -13688,19 +13688,19 @@
         <v>2</v>
       </c>
       <c r="E357" t="n">
-        <v>0.05064179348422613</v>
+        <v>0.04217454716278858</v>
       </c>
       <c r="F357" t="n">
-        <v>0.05064179348422613</v>
+        <v>0.04217454716278858</v>
       </c>
       <c r="G357" t="n">
-        <v>0.04047829787101743</v>
+        <v>0.01874484944936118</v>
       </c>
       <c r="H357" t="n">
-        <v>0.04047829787101743</v>
+        <v>0.01874484944936118</v>
       </c>
       <c r="I357" t="n">
-        <v>0.1444088282124725</v>
+        <v>0.1388074361620886</v>
       </c>
       <c r="J357" t="b">
         <v>1</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>8.538456174604281</v>
+        <v>7.882050420841313</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -13769,22 +13769,22 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>135659</v>
+        <v>136162</v>
       </c>
       <c r="E359" t="n">
-        <v>0.7521957355060378</v>
+        <v>0.7588005818436464</v>
       </c>
       <c r="F359" t="n">
-        <v>0.7521957355060378</v>
+        <v>0.7588005818436464</v>
       </c>
       <c r="G359" t="n">
-        <v>0.8010680712645251</v>
+        <v>0.8076732982623857</v>
       </c>
       <c r="H359" t="n">
-        <v>0.8010680712645251</v>
+        <v>0.8076732982623857</v>
       </c>
       <c r="I359" t="n">
-        <v>2.243244834267261</v>
+        <v>2.233761628174747</v>
       </c>
       <c r="J359" t="b">
         <v>1</v>
@@ -13797,7 +13797,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -13816,22 +13816,22 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>111763</v>
+        <v>114635</v>
       </c>
       <c r="E360" t="n">
-        <v>0.1277393769610698</v>
+        <v>0.1144477494464763</v>
       </c>
       <c r="F360" t="n">
-        <v>0.1277393769610698</v>
+        <v>0.1144477494464763</v>
       </c>
       <c r="G360" t="n">
-        <v>0.07032227364384223</v>
+        <v>0.0735937291429381</v>
       </c>
       <c r="H360" t="n">
-        <v>0.07032227364384223</v>
+        <v>0.0735937291429381</v>
       </c>
       <c r="I360" t="n">
-        <v>1.24850081435747</v>
+        <v>1.235229837755955</v>
       </c>
       <c r="J360" t="b">
         <v>1</v>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -13863,22 +13863,22 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>116802</v>
+        <v>119769</v>
       </c>
       <c r="E361" t="n">
-        <v>0.01712593500131284</v>
+        <v>0.01625253830391513</v>
       </c>
       <c r="F361" t="n">
-        <v>0.01712593500131284</v>
+        <v>0.01625253830391513</v>
       </c>
       <c r="G361" t="n">
-        <v>-0.04082228541199878</v>
+        <v>-0.06154026638840052</v>
       </c>
       <c r="H361" t="n">
-        <v>0.04082228541199878</v>
+        <v>0.06154026638840052</v>
       </c>
       <c r="I361" t="n">
-        <v>1.321247779522349</v>
+        <v>1.301704115945029</v>
       </c>
       <c r="J361" t="b">
         <v>1</v>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -13910,22 +13910,22 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>132624</v>
+        <v>131690</v>
       </c>
       <c r="E362" t="n">
-        <v>0.6740606081809954</v>
+        <v>0.6739033791879865</v>
       </c>
       <c r="F362" t="n">
-        <v>0.6740606081809954</v>
+        <v>0.6739033791879865</v>
       </c>
       <c r="G362" t="n">
-        <v>0.6668828963968295</v>
+        <v>0.651871073635212</v>
       </c>
       <c r="H362" t="n">
-        <v>0.6668828963968295</v>
+        <v>0.651871073635212</v>
       </c>
       <c r="I362" t="n">
-        <v>2.544334571751661</v>
+        <v>2.544970739325857</v>
       </c>
       <c r="J362" t="b">
         <v>1</v>
@@ -13938,7 +13938,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -13957,22 +13957,22 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>14576</v>
+        <v>13736</v>
       </c>
       <c r="E363" t="n">
-        <v>0.6092091687672594</v>
+        <v>0.6117706313697364</v>
       </c>
       <c r="F363" t="n">
-        <v>0.6092091687672594</v>
+        <v>0.6117706313697364</v>
       </c>
       <c r="G363" t="n">
-        <v>0.2502998766277856</v>
+        <v>0.231589117602093</v>
       </c>
       <c r="H363" t="n">
-        <v>0.2502998766277856</v>
+        <v>0.231589117602093</v>
       </c>
       <c r="I363" t="n">
-        <v>1.771138599750918</v>
+        <v>1.779395745513849</v>
       </c>
       <c r="J363" t="b">
         <v>1</v>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14004,22 +14004,22 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>8799</v>
+        <v>8746</v>
       </c>
       <c r="E364" t="n">
-        <v>0.7388928923811818</v>
+        <v>0.7457791892116421</v>
       </c>
       <c r="F364" t="n">
-        <v>0.7388928923811818</v>
+        <v>0.7457791892116421</v>
       </c>
       <c r="G364" t="n">
-        <v>0.807097244889325</v>
+        <v>0.8141078642885795</v>
       </c>
       <c r="H364" t="n">
-        <v>0.807097244889325</v>
+        <v>0.8141078642885795</v>
       </c>
       <c r="I364" t="n">
-        <v>1.666498593675722</v>
+        <v>1.6611387410076</v>
       </c>
       <c r="J364" t="b">
         <v>1</v>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14051,22 +14051,22 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>136048</v>
+        <v>139086</v>
       </c>
       <c r="E365" t="n">
-        <v>0.6128793108337141</v>
+        <v>0.6150654207372034</v>
       </c>
       <c r="F365" t="n">
-        <v>0.6128793108337141</v>
+        <v>0.6150654207372034</v>
       </c>
       <c r="G365" t="n">
-        <v>0.239004093752739</v>
+        <v>0.2198653262282428</v>
       </c>
       <c r="H365" t="n">
-        <v>0.239004093752739</v>
+        <v>0.2198653262282428</v>
       </c>
       <c r="I365" t="n">
-        <v>2.073942576412059</v>
+        <v>2.067356080648773</v>
       </c>
       <c r="J365" t="b">
         <v>1</v>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14116,7 +14116,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -14135,7 +14135,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>18177</v>
+        <v>23914</v>
       </c>
       <c r="E367" t="inlineStr"/>
       <c r="F367" t="inlineStr"/>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Removed: identifier, label, or future/target leakage column</t>
+          <t>Removed: identifier/label/leakage</t>
         </is>
       </c>
     </row>
@@ -14175,19 +14175,19 @@
         <v>5</v>
       </c>
       <c r="E368" t="n">
-        <v>0.6588637560132964</v>
+        <v>0.660903390861731</v>
       </c>
       <c r="F368" t="n">
-        <v>0.6588637560132964</v>
+        <v>0.660903390861731</v>
       </c>
       <c r="G368" t="n">
-        <v>0.3444383954078802</v>
+        <v>0.3340619963436204</v>
       </c>
       <c r="H368" t="n">
-        <v>0.3444383954078802</v>
+        <v>0.3340619963436204</v>
       </c>
       <c r="I368" t="n">
-        <v>0.6152960549762565</v>
+        <v>0.6039378544154688</v>
       </c>
       <c r="J368" t="b">
         <v>1</v>
@@ -14200,7 +14200,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -14219,22 +14219,22 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>106810</v>
+        <v>106392</v>
       </c>
       <c r="E369" t="n">
-        <v>0.9584260176526948</v>
+        <v>0.9593346399207043</v>
       </c>
       <c r="F369" t="n">
-        <v>0.9584260176526948</v>
+        <v>0.9593346399207043</v>
       </c>
       <c r="G369" t="n">
-        <v>0.9211920889226393</v>
+        <v>0.923307153587663</v>
       </c>
       <c r="H369" t="n">
-        <v>0.9211920889226393</v>
+        <v>0.923307153587663</v>
       </c>
       <c r="I369" t="n">
-        <v>1.778284058914192</v>
+        <v>1.756529921230553</v>
       </c>
       <c r="J369" t="b">
         <v>1</v>
@@ -14247,7 +14247,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14269,19 +14269,19 @@
         <v>4</v>
       </c>
       <c r="E370" t="n">
-        <v>0.01400399798109835</v>
+        <v>0.01683312462997215</v>
       </c>
       <c r="F370" t="n">
-        <v>0.01400399798109835</v>
+        <v>0.01683312462997215</v>
       </c>
       <c r="G370" t="n">
-        <v>0.02470631843845178</v>
+        <v>0.03115033091576453</v>
       </c>
       <c r="H370" t="n">
-        <v>0.02470631843845178</v>
+        <v>0.03115033091576453</v>
       </c>
       <c r="I370" t="n">
-        <v>0.04749268024642728</v>
+        <v>0.0488380993819173</v>
       </c>
       <c r="J370" t="b">
         <v>1</v>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Candidate: passed missingness, leakage, and variance checks</t>
+          <t>Candidate: passed quality checks</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14313,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>139568</v>
+        <v>142820</v>
       </c>
       <c r="E371" t="inlineStr"/>
       <c r="F371" t="inlineStr"/>
@@ -14350,22 +14350,22 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>18177</v>
+        <v>23914</v>
       </c>
       <c r="E372" t="n">
-        <v>0.3875838198267958</v>
+        <v>0.246877270044194</v>
       </c>
       <c r="F372" t="n">
-        <v>0.3875838198267958</v>
+        <v>0.246877270044194</v>
       </c>
       <c r="G372" t="n">
-        <v>0.2923438618005575</v>
+        <v>0.2382128298820489</v>
       </c>
       <c r="H372" t="n">
-        <v>0.2923438618005575</v>
+        <v>0.2382128298820489</v>
       </c>
       <c r="I372" t="n">
-        <v>1.254319952115257</v>
+        <v>1.338734411808855</v>
       </c>
       <c r="J372" t="b">
         <v>1</v>
@@ -14378,7 +14378,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14415,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Removed: constant or near-constant column</t>
+          <t>Removed: constant column</t>
         </is>
       </c>
     </row>
@@ -14434,22 +14434,22 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>106810</v>
+        <v>106392</v>
       </c>
       <c r="E374" t="n">
-        <v>0.9584260176325337</v>
+        <v>0.959334639901136</v>
       </c>
       <c r="F374" t="n">
-        <v>0.9584260176325337</v>
+        <v>0.959334639901136</v>
       </c>
       <c r="G374" t="n">
-        <v>0.9211920889226393</v>
+        <v>0.923307153587663</v>
       </c>
       <c r="H374" t="n">
-        <v>0.9211920889226393</v>
+        <v>0.923307153587663</v>
       </c>
       <c r="I374" t="n">
-        <v>1.778297423232086</v>
+        <v>1.756683838051794</v>
       </c>
       <c r="J374" t="b">
         <v>1</v>
@@ -14462,7 +14462,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14481,22 +14481,22 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>523534</v>
+        <v>524432</v>
       </c>
       <c r="E375" t="n">
-        <v>0.7161354432720102</v>
+        <v>0.7166676925967517</v>
       </c>
       <c r="F375" t="n">
-        <v>0.7161354432720102</v>
+        <v>0.7166676925967517</v>
       </c>
       <c r="G375" t="n">
-        <v>0.7944951838820224</v>
+        <v>0.7710330645688364</v>
       </c>
       <c r="H375" t="n">
-        <v>0.7944951838820224</v>
+        <v>0.7710330645688364</v>
       </c>
       <c r="I375" t="n">
-        <v>2.566158918494872</v>
+        <v>2.574539226984718</v>
       </c>
       <c r="J375" t="b">
         <v>1</v>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Selected: domain-relevant battery/energy feature and passed quality checks</t>
+          <t>Selected: domain-relevant battery/energy feature</t>
         </is>
       </c>
     </row>
@@ -14528,7 +14528,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>530123</v>
+        <v>531595</v>
       </c>
       <c r="E376" t="inlineStr"/>
       <c r="F376" t="inlineStr"/>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Removed: identifier, label, or future/target leakage column</t>
+          <t>Removed: identifier/label/leakage</t>
         </is>
       </c>
     </row>
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>560091</v>
+        <v>560877</v>
       </c>
       <c r="E377" t="inlineStr"/>
       <c r="F377" t="inlineStr"/>
@@ -14583,7 +14583,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Removed: identifier, label, or future/target leakage column</t>
+          <t>Removed: identifier/label/leakage</t>
         </is>
       </c>
     </row>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Removed: identifier, label, or future/target leakage column</t>
+          <t>Removed: identifier/label/leakage</t>
         </is>
       </c>
     </row>
@@ -14639,7 +14639,7 @@
         </is>
       </c>
       <c r="D379" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E379" t="inlineStr"/>
       <c r="F379" t="inlineStr"/>
@@ -14657,7 +14657,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Removed: identifier, label, or future/target leakage column</t>
+          <t>Removed: identifier/label/leakage</t>
         </is>
       </c>
     </row>
